--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][CI]Yearly_U_test.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][CI]Yearly_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sd_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_P2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sd_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>U_statistic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -488,28 +500,28 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>8.359303696114377</v>
+        <v>8.115964009832501</v>
       </c>
       <c r="D2" t="n">
-        <v>4.737474713760621</v>
+        <v>4.941204153741769</v>
       </c>
       <c r="E2" t="n">
         <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>9.803930251711241</v>
+        <v>9.273629778319208</v>
       </c>
       <c r="G2" t="n">
-        <v>2.01980623296222</v>
+        <v>1.305434213870191</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3395833307020266</v>
+        <v>0.5969127254582774</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -528,31 +540,31 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>5.891767158363107</v>
+        <v>5.686151183361217</v>
       </c>
       <c r="D3" t="n">
-        <v>3.605181945739701</v>
+        <v>3.277584805332002</v>
       </c>
       <c r="E3" t="n">
         <v>31</v>
       </c>
       <c r="F3" t="n">
-        <v>13.56509830945829</v>
+        <v>12.99791045100299</v>
       </c>
       <c r="G3" t="n">
-        <v>3.287249174217373</v>
+        <v>2.964466655554892</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4621601141622e-07</v>
+        <v>1.461499091465625e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3864803424866e-06</v>
+        <v>4.384497274396875e-06</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -568,31 +580,31 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>8.309760229194842</v>
+        <v>8.441607838272898</v>
       </c>
       <c r="D4" t="n">
-        <v>3.285970780924887</v>
+        <v>3.33885346652403</v>
       </c>
       <c r="E4" t="n">
         <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>12.34217548695376</v>
+        <v>11.89210827169041</v>
       </c>
       <c r="G4" t="n">
-        <v>3.09451216545543</v>
+        <v>2.934136625986556</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001500320566091887</v>
+        <v>0.001354474195866209</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00450096169827566</v>
+        <v>0.04063422587598626</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -608,31 +620,31 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>8.51356735612592</v>
+        <v>8.375752725324753</v>
       </c>
       <c r="D5" t="n">
-        <v>3.44637212062906</v>
+        <v>3.341191830053104</v>
       </c>
       <c r="E5" t="n">
         <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>16.65259442124849</v>
+        <v>16.70267614659169</v>
       </c>
       <c r="G5" t="n">
-        <v>1.108701240705837</v>
+        <v>1.133270836184869</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.652105483629477e-09</v>
+        <v>8.659979663152756e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.956316450888431e-08</v>
+        <v>2.597993898945827e-07</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -648,31 +660,31 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>10.40534460770274</v>
+        <v>10.04581497052219</v>
       </c>
       <c r="D6" t="n">
-        <v>4.256741846099621</v>
+        <v>4.361439928845285</v>
       </c>
       <c r="E6" t="n">
         <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>13.05346024980336</v>
+        <v>13.26293105150384</v>
       </c>
       <c r="G6" t="n">
-        <v>2.226608665650465</v>
+        <v>2.241636196894367</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0124753505486087</v>
+        <v>0.0056287163449574</v>
       </c>
       <c r="K6" t="n">
-        <v>0.374260516458261</v>
+        <v>0.168861490348722</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -688,34 +700,34 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>7.227922232844764</v>
+        <v>6.995755814633445</v>
       </c>
       <c r="D7" t="n">
-        <v>4.7852106289876</v>
+        <v>4.56290330175869</v>
       </c>
       <c r="E7" t="n">
         <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>10.28930950329073</v>
+        <v>9.904369452029608</v>
       </c>
       <c r="G7" t="n">
-        <v>1.810436561404523</v>
+        <v>1.374789113536427</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001718163657837091</v>
+        <v>0.001260079759530211</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05154490973511272</v>
+        <v>0.03780239278590632</v>
       </c>
       <c r="L7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -728,31 +740,31 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>7.829767996723016</v>
+        <v>7.793276801005045</v>
       </c>
       <c r="D8" t="n">
-        <v>2.936872495813177</v>
+        <v>2.927217131977367</v>
       </c>
       <c r="E8" t="n">
         <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>13.32621002348557</v>
+        <v>13.08047726303645</v>
       </c>
       <c r="G8" t="n">
-        <v>2.353663038416523</v>
+        <v>2.321850302510859</v>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
         <v>43</v>
       </c>
       <c r="J8" t="n">
-        <v>2.725454136967009e-07</v>
+        <v>1.039326669553609e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>8.176362410901027e-06</v>
+        <v>3.117980008660827e-05</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -768,31 +780,31 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>8.505443592236235</v>
+        <v>8.32940849379017</v>
       </c>
       <c r="D9" t="n">
-        <v>5.409092600187161</v>
+        <v>5.305034391292501</v>
       </c>
       <c r="E9" t="n">
         <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>14.0485858051437</v>
+        <v>14.35098601285862</v>
       </c>
       <c r="G9" t="n">
-        <v>2.232349780420773</v>
+        <v>2.114782051043653</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I9" t="n">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001751280605492681</v>
+        <v>3.207984117294382e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005253841816478042</v>
+        <v>0.0009623952351883145</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -808,31 +820,31 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>9.045213195332908</v>
+        <v>8.901533894193713</v>
       </c>
       <c r="D10" t="n">
-        <v>3.756325079492834</v>
+        <v>3.669461476928005</v>
       </c>
       <c r="E10" t="n">
         <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>14.57310909927146</v>
+        <v>14.16897936254051</v>
       </c>
       <c r="G10" t="n">
-        <v>2.494844457700568</v>
+        <v>2.297643874668191</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J10" t="n">
-        <v>4.198421074370363e-06</v>
+        <v>9.520628782635424e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0001259526322311109</v>
+        <v>0.0002856188634790627</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -848,31 +860,31 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>9.621347861386136</v>
+        <v>9.4260609613283</v>
       </c>
       <c r="D11" t="n">
-        <v>3.689158906098355</v>
+        <v>3.741011248806899</v>
       </c>
       <c r="E11" t="n">
         <v>31</v>
       </c>
       <c r="F11" t="n">
-        <v>14.51213156947647</v>
+        <v>14.19181735505178</v>
       </c>
       <c r="G11" t="n">
-        <v>3.487919119406177</v>
+        <v>3.527996368123342</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002975978797901522</v>
+        <v>0.0006458965997800412</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008927936393704566</v>
+        <v>0.01937689799340124</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -888,31 +900,31 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>8.086941355352748</v>
+        <v>7.921891331970277</v>
       </c>
       <c r="D12" t="n">
-        <v>3.805203957343498</v>
+        <v>3.604864384190747</v>
       </c>
       <c r="E12" t="n">
         <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>16.52489462491731</v>
+        <v>16.16959279940755</v>
       </c>
       <c r="G12" t="n">
-        <v>1.98751856317444</v>
+        <v>1.743476831585784</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>5.345509575019857e-09</v>
+        <v>9.789112615601505e-09</v>
       </c>
       <c r="K12" t="n">
-        <v>1.603652872505957e-07</v>
+        <v>2.936733784680451e-07</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -928,28 +940,28 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>11.51004350392402</v>
+        <v>11.34269103171151</v>
       </c>
       <c r="D13" t="n">
-        <v>3.384311709098484</v>
+        <v>3.375676707780485</v>
       </c>
       <c r="E13" t="n">
         <v>31</v>
       </c>
       <c r="F13" t="n">
-        <v>11.35512244892375</v>
+        <v>11.44775368932645</v>
       </c>
       <c r="G13" t="n">
-        <v>2.081477933116283</v>
+        <v>2.054094951854632</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="J13" t="n">
-        <v>0.692473599299549</v>
+        <v>0.9917264707961607</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -968,31 +980,31 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>7.569687044702341</v>
+        <v>7.505658478657017</v>
       </c>
       <c r="D14" t="n">
-        <v>2.837789443256526</v>
+        <v>2.782897165471232</v>
       </c>
       <c r="E14" t="n">
         <v>31</v>
       </c>
       <c r="F14" t="n">
-        <v>12.25894007067127</v>
+        <v>11.71971339817487</v>
       </c>
       <c r="G14" t="n">
-        <v>4.744558117335893</v>
+        <v>4.678890951937652</v>
       </c>
       <c r="H14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
         <v>171</v>
       </c>
       <c r="J14" t="n">
-        <v>0.007539176511118984</v>
+        <v>0.02578423491765985</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2261752953335695</v>
+        <v>0.7735270475297955</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1008,31 +1020,31 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>11.40129021807258</v>
+        <v>11.38648878090811</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150823553685282</v>
+        <v>2.173129175641999</v>
       </c>
       <c r="E15" t="n">
         <v>31</v>
       </c>
       <c r="F15" t="n">
-        <v>14.30121741024087</v>
+        <v>14.1927290379966</v>
       </c>
       <c r="G15" t="n">
-        <v>1.826159439347799</v>
+        <v>1.810889268670729</v>
       </c>
       <c r="H15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J15" t="n">
-        <v>2.099465677690392e-05</v>
+        <v>7.141400738135679e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0006298397033071176</v>
+        <v>0.002142420221440704</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -1048,31 +1060,31 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>8.771658538681958</v>
+        <v>8.573422976625583</v>
       </c>
       <c r="D16" t="n">
-        <v>3.092981240686745</v>
+        <v>3.273184571343716</v>
       </c>
       <c r="E16" t="n">
         <v>31</v>
       </c>
       <c r="F16" t="n">
-        <v>11.97376696087142</v>
+        <v>11.88137262413709</v>
       </c>
       <c r="G16" t="n">
-        <v>1.41902841380995</v>
+        <v>1.454533602878788</v>
       </c>
       <c r="H16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J16" t="n">
-        <v>7.968083572110736e-05</v>
+        <v>0.0001815500411740529</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002390425071633221</v>
+        <v>0.005446501235221588</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1088,31 +1100,31 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>10.52705590818531</v>
+        <v>10.75067182400198</v>
       </c>
       <c r="D17" t="n">
-        <v>3.188086598667641</v>
+        <v>3.034844792845496</v>
       </c>
       <c r="E17" t="n">
         <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>14.95055788918738</v>
+        <v>14.42241438281786</v>
       </c>
       <c r="G17" t="n">
-        <v>3.298775198878263</v>
+        <v>3.044132163370253</v>
       </c>
       <c r="H17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0001751280605492681</v>
+        <v>0.0009400645496222086</v>
       </c>
       <c r="K17" t="n">
-        <v>0.005253841816478042</v>
+        <v>0.02820193648866626</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1128,31 +1140,31 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>9.109068065864159</v>
+        <v>8.749898487868016</v>
       </c>
       <c r="D18" t="n">
-        <v>5.12783302990974</v>
+        <v>5.173947199382524</v>
       </c>
       <c r="E18" t="n">
         <v>31</v>
       </c>
       <c r="F18" t="n">
-        <v>13.67136286055616</v>
+        <v>13.28951659256932</v>
       </c>
       <c r="G18" t="n">
-        <v>3.280099109108086</v>
+        <v>3.239278246692852</v>
       </c>
       <c r="H18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I18" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0007610736202452088</v>
+        <v>0.0007514281649849018</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02283220860735627</v>
+        <v>0.02254284494954705</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1168,31 +1180,31 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>9.064719366204633</v>
+        <v>8.663270845758248</v>
       </c>
       <c r="D19" t="n">
-        <v>4.589812781773144</v>
+        <v>4.890975023712057</v>
       </c>
       <c r="E19" t="n">
         <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>13.16239935967082</v>
+        <v>12.70835293780769</v>
       </c>
       <c r="G19" t="n">
-        <v>3.362315992377631</v>
+        <v>3.240174014668046</v>
       </c>
       <c r="H19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="J19" t="n">
-        <v>0.003923355770258245</v>
+        <v>0.007699613999927837</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1177006731077474</v>
+        <v>0.2309884199978351</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1208,31 +1220,31 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>9.926613840045269</v>
+        <v>10.03901784156472</v>
       </c>
       <c r="D20" t="n">
-        <v>2.94402657782383</v>
+        <v>2.893717997755632</v>
       </c>
       <c r="E20" t="n">
         <v>31</v>
       </c>
       <c r="F20" t="n">
-        <v>14.9497031362151</v>
+        <v>14.91712316361176</v>
       </c>
       <c r="G20" t="n">
-        <v>2.145100603129499</v>
+        <v>2.213843013305308</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I20" t="n">
         <v>47</v>
       </c>
       <c r="J20" t="n">
-        <v>4.098287166081066e-07</v>
+        <v>1.578072018701653e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>1.22948614982432e-05</v>
+        <v>4.734216056104959e-05</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -1248,31 +1260,31 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>8.779536256793383</v>
+        <v>8.331691460184988</v>
       </c>
       <c r="D21" t="n">
-        <v>3.831857935518981</v>
+        <v>3.742016673379655</v>
       </c>
       <c r="E21" t="n">
         <v>31</v>
       </c>
       <c r="F21" t="n">
-        <v>12.8968973354409</v>
+        <v>12.81934401560188</v>
       </c>
       <c r="G21" t="n">
-        <v>2.128758387472451</v>
+        <v>2.22914913183672</v>
       </c>
       <c r="H21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I21" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J21" t="n">
-        <v>6.778101584433548e-05</v>
+        <v>3.207984117294382e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.002033430475330065</v>
+        <v>0.0009623952351883145</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -1288,31 +1300,31 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>7.950992007657781</v>
+        <v>7.92520791930077</v>
       </c>
       <c r="D22" t="n">
-        <v>3.022777467328742</v>
+        <v>3.027916614032713</v>
       </c>
       <c r="E22" t="n">
         <v>31</v>
       </c>
       <c r="F22" t="n">
-        <v>16.53144222549692</v>
+        <v>16.38186433049612</v>
       </c>
       <c r="G22" t="n">
-        <v>3.334076702345949</v>
+        <v>3.480703445138517</v>
       </c>
       <c r="H22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I22" t="n">
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>1.669997572540146e-08</v>
+        <v>5.852263655702324e-08</v>
       </c>
       <c r="K22" t="n">
-        <v>5.009992717620437e-07</v>
+        <v>1.755679096710697e-06</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -1328,31 +1340,31 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>6.770270271036051</v>
+        <v>6.89771745655711</v>
       </c>
       <c r="D23" t="n">
-        <v>2.9689676776768</v>
+        <v>3.139710605632082</v>
       </c>
       <c r="E23" t="n">
         <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>11.24776475256254</v>
+        <v>11.25592583110858</v>
       </c>
       <c r="G23" t="n">
-        <v>1.964825511657701</v>
+        <v>2.065489033808432</v>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J23" t="n">
-        <v>1.632951325855289e-06</v>
+        <v>1.531637591240853e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>4.898853977565866e-05</v>
+        <v>0.0004594912773722558</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1368,31 +1380,31 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>12.89235141559415</v>
+        <v>12.56748130508615</v>
       </c>
       <c r="D24" t="n">
-        <v>2.637428549960091</v>
+        <v>3.029916193791098</v>
       </c>
       <c r="E24" t="n">
         <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>16.68266481228282</v>
+        <v>16.7692903580236</v>
       </c>
       <c r="G24" t="n">
-        <v>1.654199634542526</v>
+        <v>1.716748846738176</v>
       </c>
       <c r="H24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I24" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="J24" t="n">
-        <v>3.174590564650748e-06</v>
+        <v>4.354636100083719e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>9.523771693952245e-05</v>
+        <v>0.0001306390830025116</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -1408,31 +1420,31 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>9.333753000280533</v>
+        <v>9.456680443762172</v>
       </c>
       <c r="D25" t="n">
-        <v>3.479238612944298</v>
+        <v>3.381254641506168</v>
       </c>
       <c r="E25" t="n">
         <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>13.06544812834026</v>
+        <v>12.86569208620265</v>
       </c>
       <c r="G25" t="n">
-        <v>2.683012317349343</v>
+        <v>2.739051702580442</v>
       </c>
       <c r="H25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0004624285698355455</v>
+        <v>0.001455354162976677</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01387285709506637</v>
+        <v>0.0436606248893003</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
@@ -1448,31 +1460,31 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>10.70747235935388</v>
+        <v>10.3864352579102</v>
       </c>
       <c r="D26" t="n">
-        <v>2.58165793321517</v>
+        <v>3.111668079082705</v>
       </c>
       <c r="E26" t="n">
         <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>16.12357959802565</v>
+        <v>16.08274978085651</v>
       </c>
       <c r="G26" t="n">
-        <v>1.959937682449586</v>
+        <v>1.926507449964502</v>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>1.063443889597435e-08</v>
+        <v>2.894659292479515e-08</v>
       </c>
       <c r="K26" t="n">
-        <v>3.190331668792304e-07</v>
+        <v>8.683977877438546e-07</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1488,31 +1500,31 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>5.637937689913248</v>
+        <v>5.757352166775954</v>
       </c>
       <c r="D27" t="n">
-        <v>3.498712484094494</v>
+        <v>3.687354966204548</v>
       </c>
       <c r="E27" t="n">
         <v>31</v>
       </c>
       <c r="F27" t="n">
-        <v>15.07243348468037</v>
+        <v>15.02114016223964</v>
       </c>
       <c r="G27" t="n">
-        <v>2.630120660230482</v>
+        <v>2.766255566022476</v>
       </c>
       <c r="H27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>7.551976616635313e-09</v>
+        <v>5.209827400341707e-08</v>
       </c>
       <c r="K27" t="n">
-        <v>2.265592984990594e-07</v>
+        <v>1.562948220102512e-06</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1528,31 +1540,31 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>7.860152089264581</v>
+        <v>7.503979559221139</v>
       </c>
       <c r="D28" t="n">
-        <v>3.335846130091778</v>
+        <v>3.434958326358458</v>
       </c>
       <c r="E28" t="n">
         <v>31</v>
       </c>
       <c r="F28" t="n">
-        <v>13.51650030774171</v>
+        <v>13.2320737146547</v>
       </c>
       <c r="G28" t="n">
-        <v>4.005239103675433</v>
+        <v>4.115605832259205</v>
       </c>
       <c r="H28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I28" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="J28" t="n">
-        <v>8.6346719096313e-05</v>
+        <v>0.0001971375739483935</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00259040157288939</v>
+        <v>0.005914127218451804</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
@@ -1568,31 +1580,31 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>7.15798353744587</v>
+        <v>7.013961189953032</v>
       </c>
       <c r="D29" t="n">
-        <v>3.268001971707853</v>
+        <v>3.146690204758047</v>
       </c>
       <c r="E29" t="n">
         <v>31</v>
       </c>
       <c r="F29" t="n">
-        <v>17.65281234215701</v>
+        <v>17.71663219613605</v>
       </c>
       <c r="G29" t="n">
-        <v>1.843162823239965</v>
+        <v>1.932335664867001</v>
       </c>
       <c r="H29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>2.652105483629477e-09</v>
+        <v>8.659979663152756e-09</v>
       </c>
       <c r="K29" t="n">
-        <v>7.956316450888431e-08</v>
+        <v>2.597993898945827e-07</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1608,31 +1620,31 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>10.09272455854572</v>
+        <v>10.00988588422064</v>
       </c>
       <c r="D30" t="n">
-        <v>5.444311382488721</v>
+        <v>5.43551741399228</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>14.70847055305004</v>
+        <v>14.01305928901528</v>
       </c>
       <c r="G30" t="n">
-        <v>4.548574678225497</v>
+        <v>4.260563083927168</v>
       </c>
       <c r="H30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I30" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J30" t="n">
-        <v>0.005306798846624329</v>
+        <v>0.01756705445010766</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1592039653987299</v>
+        <v>0.5270116335032299</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1648,31 +1660,31 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>10.84917487561047</v>
+        <v>10.6906514211792</v>
       </c>
       <c r="D31" t="n">
-        <v>3.589202040291211</v>
+        <v>3.710206714923053</v>
       </c>
       <c r="E31" t="n">
         <v>31</v>
       </c>
       <c r="F31" t="n">
-        <v>14.98232221578326</v>
+        <v>14.74225362633603</v>
       </c>
       <c r="G31" t="n">
-        <v>2.082582396263377</v>
+        <v>2.030340927894141</v>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I31" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J31" t="n">
-        <v>2.955472149467701e-05</v>
+        <v>0.000100837064268563</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0008866416448403104</v>
+        <v>0.003025111928056891</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -1688,31 +1700,31 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>71.50047083908244</v>
+        <v>71.35539529675184</v>
       </c>
       <c r="D32" t="n">
-        <v>13.2639099860289</v>
+        <v>13.2297839558516</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
       </c>
       <c r="F32" t="n">
-        <v>82.75494501991724</v>
+        <v>83.19251992621156</v>
       </c>
       <c r="G32" t="n">
-        <v>4.723507945360254</v>
+        <v>4.779566273237065</v>
       </c>
       <c r="H32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I32" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="J32" t="n">
-        <v>0.002533526438869483</v>
+        <v>0.001801006152869858</v>
       </c>
       <c r="K32" t="n">
-        <v>0.07600579316608448</v>
+        <v>0.05403018458609575</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1728,31 +1740,31 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>69.61055726994225</v>
+        <v>69.55316073522253</v>
       </c>
       <c r="D33" t="n">
-        <v>10.50412767032952</v>
+        <v>10.48338937884257</v>
       </c>
       <c r="E33" t="n">
         <v>31</v>
       </c>
       <c r="F33" t="n">
-        <v>75.30550420571494</v>
+        <v>74.55348661458414</v>
       </c>
       <c r="G33" t="n">
-        <v>5.222739176702413</v>
+        <v>4.955395851692573</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I33" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J33" t="n">
-        <v>0.01811025012501557</v>
+        <v>0.03183390510613443</v>
       </c>
       <c r="K33" t="n">
-        <v>0.543307503750467</v>
+        <v>0.9550171531840329</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1768,31 +1780,31 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>74.19080397850223</v>
+        <v>73.92394208715335</v>
       </c>
       <c r="D34" t="n">
-        <v>8.447804663517759</v>
+        <v>8.512345997636103</v>
       </c>
       <c r="E34" t="n">
         <v>31</v>
       </c>
       <c r="F34" t="n">
-        <v>84.25620370819827</v>
+        <v>84.09470616713878</v>
       </c>
       <c r="G34" t="n">
-        <v>5.704702117747697</v>
+        <v>5.740740108408538</v>
       </c>
       <c r="H34" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I34" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="J34" t="n">
-        <v>9.353710291066545e-05</v>
+        <v>0.0001815500411740529</v>
       </c>
       <c r="K34" t="n">
-        <v>0.002806113087319963</v>
+        <v>0.005446501235221588</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1808,28 +1820,28 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>77.65785511667691</v>
+        <v>77.54766667049705</v>
       </c>
       <c r="D35" t="n">
-        <v>7.730323019312896</v>
+        <v>7.903904333175229</v>
       </c>
       <c r="E35" t="n">
         <v>31</v>
       </c>
       <c r="F35" t="n">
-        <v>74.11995651668006</v>
+        <v>74.25114734588385</v>
       </c>
       <c r="G35" t="n">
-        <v>5.656708908707316</v>
+        <v>5.88151299371424</v>
       </c>
       <c r="H35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I35" t="n">
-        <v>395</v>
+        <v>353</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1030521545530955</v>
+        <v>0.1274290453225189</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1848,31 +1860,31 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>72.60867021670009</v>
+        <v>72.83524453573293</v>
       </c>
       <c r="D36" t="n">
-        <v>8.956531742682866</v>
+        <v>9.204002069409004</v>
       </c>
       <c r="E36" t="n">
         <v>31</v>
       </c>
       <c r="F36" t="n">
-        <v>83.22868331293381</v>
+        <v>83.35239217483881</v>
       </c>
       <c r="G36" t="n">
-        <v>5.35489933561694</v>
+        <v>5.621529113488369</v>
       </c>
       <c r="H36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I36" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J36" t="n">
-        <v>9.353710291066545e-05</v>
+        <v>0.0003203996122224882</v>
       </c>
       <c r="K36" t="n">
-        <v>0.002806113087319963</v>
+        <v>0.009611988366674646</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -1888,31 +1900,31 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>76.09126678325123</v>
+        <v>76.02187771204619</v>
       </c>
       <c r="D37" t="n">
-        <v>9.431014773275242</v>
+        <v>9.469287740687678</v>
       </c>
       <c r="E37" t="n">
         <v>31</v>
       </c>
       <c r="F37" t="n">
-        <v>84.51554340157858</v>
+        <v>84.93118617771299</v>
       </c>
       <c r="G37" t="n">
-        <v>4.599919854025991</v>
+        <v>3.836875230924115</v>
       </c>
       <c r="H37" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I37" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="J37" t="n">
-        <v>0.001231302771999713</v>
+        <v>0.001012116276347626</v>
       </c>
       <c r="K37" t="n">
-        <v>0.03693908315999138</v>
+        <v>0.03036348829042879</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -1928,31 +1940,31 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>71.76527449804288</v>
+        <v>70.95003634056782</v>
       </c>
       <c r="D38" t="n">
-        <v>11.48848289911247</v>
+        <v>10.96623787558978</v>
       </c>
       <c r="E38" t="n">
         <v>31</v>
       </c>
       <c r="F38" t="n">
-        <v>78.93763171429308</v>
+        <v>79.12362916514007</v>
       </c>
       <c r="G38" t="n">
-        <v>6.278309979761166</v>
+        <v>6.55662448082452</v>
       </c>
       <c r="H38" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I38" t="n">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0330196880933975</v>
+        <v>0.01481637758900041</v>
       </c>
       <c r="K38" t="n">
-        <v>0.9905906428019249</v>
+        <v>0.4444913276700123</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1968,31 +1980,31 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>63.49625583678498</v>
+        <v>63.62421706590222</v>
       </c>
       <c r="D39" t="n">
-        <v>8.951401049783192</v>
+        <v>8.805746878936651</v>
       </c>
       <c r="E39" t="n">
         <v>31</v>
       </c>
       <c r="F39" t="n">
-        <v>71.38600623847027</v>
+        <v>72.21594020797437</v>
       </c>
       <c r="G39" t="n">
-        <v>7.682827715144072</v>
+        <v>7.65129448509821</v>
       </c>
       <c r="H39" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I39" t="n">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="J39" t="n">
-        <v>0.004431755717731556</v>
+        <v>0.002548442929003083</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1329526715319467</v>
+        <v>0.07645328787009248</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -2008,28 +2020,28 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>71.86686867494898</v>
+        <v>71.65626194945597</v>
       </c>
       <c r="D40" t="n">
-        <v>9.018077097121553</v>
+        <v>9.049247110810525</v>
       </c>
       <c r="E40" t="n">
         <v>31</v>
       </c>
       <c r="F40" t="n">
-        <v>72.20604020546395</v>
+        <v>72.14661142611538</v>
       </c>
       <c r="G40" t="n">
-        <v>7.430213106663319</v>
+        <v>7.829738726544088</v>
       </c>
       <c r="H40" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I40" t="n">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6782933410999001</v>
+        <v>0.6556772632177376</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -2048,28 +2060,28 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>73.17030089572668</v>
+        <v>72.32202738811597</v>
       </c>
       <c r="D41" t="n">
-        <v>11.60555573587201</v>
+        <v>11.92689564703834</v>
       </c>
       <c r="E41" t="n">
         <v>31</v>
       </c>
       <c r="F41" t="n">
-        <v>78.01213265747377</v>
+        <v>78.10079927032751</v>
       </c>
       <c r="G41" t="n">
-        <v>7.739387300914687</v>
+        <v>8.016562533151015</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I41" t="n">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1737870019066058</v>
+        <v>0.1326895549849034</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -2088,28 +2100,28 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>75.4130746150541</v>
+        <v>75.91608635088394</v>
       </c>
       <c r="D42" t="n">
-        <v>9.911175003275995</v>
+        <v>9.319277321284996</v>
       </c>
       <c r="E42" t="n">
         <v>31</v>
       </c>
       <c r="F42" t="n">
-        <v>74.83806576392996</v>
+        <v>74.89731513667711</v>
       </c>
       <c r="G42" t="n">
-        <v>5.181977993347695</v>
+        <v>5.386551053643284</v>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I42" t="n">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7649118789141331</v>
+        <v>0.7012214738223803</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2128,31 +2140,31 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>59.00270285512094</v>
+        <v>59.1326326791312</v>
       </c>
       <c r="D43" t="n">
-        <v>8.827703549250188</v>
+        <v>8.829575672018361</v>
       </c>
       <c r="E43" t="n">
         <v>31</v>
       </c>
       <c r="F43" t="n">
-        <v>82.02346744468761</v>
+        <v>81.61855536190717</v>
       </c>
       <c r="G43" t="n">
-        <v>4.597247876562444</v>
+        <v>4.668551389524951</v>
       </c>
       <c r="H43" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>2.652105483629477e-09</v>
+        <v>8.659979663152756e-09</v>
       </c>
       <c r="K43" t="n">
-        <v>7.956316450888431e-08</v>
+        <v>2.597993898945827e-07</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2168,28 +2180,28 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>77.06834100256386</v>
+        <v>77.41321399457507</v>
       </c>
       <c r="D44" t="n">
-        <v>6.944110599192746</v>
+        <v>6.461174034008178</v>
       </c>
       <c r="E44" t="n">
         <v>31</v>
       </c>
       <c r="F44" t="n">
-        <v>79.99101281739308</v>
+        <v>79.88882706884175</v>
       </c>
       <c r="G44" t="n">
-        <v>5.917431914458946</v>
+        <v>5.800781558496661</v>
       </c>
       <c r="H44" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I44" t="n">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1863179623976219</v>
+        <v>0.2412952675894003</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -2208,31 +2220,31 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>68.0194727926218</v>
+        <v>68.01296131458085</v>
       </c>
       <c r="D45" t="n">
-        <v>11.32765536681011</v>
+        <v>11.32332951603318</v>
       </c>
       <c r="E45" t="n">
         <v>31</v>
       </c>
       <c r="F45" t="n">
-        <v>80.88535351265078</v>
+        <v>80.69277728678708</v>
       </c>
       <c r="G45" t="n">
-        <v>6.497845650796986</v>
+        <v>6.808998925094</v>
       </c>
       <c r="H45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I45" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0002041333948081417</v>
+        <v>0.0004749021959969055</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00612400184424425</v>
+        <v>0.01424706587990716</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2248,31 +2260,31 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>69.04616438405428</v>
+        <v>68.75225872313725</v>
       </c>
       <c r="D46" t="n">
-        <v>11.28671184328545</v>
+        <v>10.86309958310514</v>
       </c>
       <c r="E46" t="n">
         <v>31</v>
       </c>
       <c r="F46" t="n">
-        <v>81.33582002535316</v>
+        <v>81.19266836486288</v>
       </c>
       <c r="G46" t="n">
-        <v>4.946880708205927</v>
+        <v>5.157312456891768</v>
       </c>
       <c r="H46" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I46" t="n">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0003715559713786149</v>
+        <v>0.0003469183141887698</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01114667914135845</v>
+        <v>0.0104075494256631</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
@@ -2288,31 +2300,31 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>65.23246931879939</v>
+        <v>65.68308240481349</v>
       </c>
       <c r="D47" t="n">
-        <v>9.396405333665196</v>
+        <v>9.804897880653535</v>
       </c>
       <c r="E47" t="n">
         <v>31</v>
       </c>
       <c r="F47" t="n">
-        <v>81.49531921253177</v>
+        <v>81.84099347711263</v>
       </c>
       <c r="G47" t="n">
-        <v>5.605891198892645</v>
+        <v>5.783713394993156</v>
       </c>
       <c r="H47" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I47" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J47" t="n">
-        <v>5.014702446342466e-07</v>
+        <v>2.635054954307537e-06</v>
       </c>
       <c r="K47" t="n">
-        <v>1.50441073390274e-05</v>
+        <v>7.905164862922612e-05</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2328,31 +2340,31 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>70.64619431755018</v>
+        <v>70.58022711199935</v>
       </c>
       <c r="D48" t="n">
-        <v>11.7026200480206</v>
+        <v>11.75926637368301</v>
       </c>
       <c r="E48" t="n">
         <v>31</v>
       </c>
       <c r="F48" t="n">
-        <v>78.07691340558591</v>
+        <v>77.91692309893999</v>
       </c>
       <c r="G48" t="n">
-        <v>5.927547514689101</v>
+        <v>6.21137887740838</v>
       </c>
       <c r="H48" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I48" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="J48" t="n">
-        <v>0.02586002726751929</v>
+        <v>0.03713535035672766</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7758008180255785</v>
+        <v>1</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2368,31 +2380,31 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>76.62878621081238</v>
+        <v>76.22784812102232</v>
       </c>
       <c r="D49" t="n">
-        <v>7.822828029903635</v>
+        <v>7.696549901248163</v>
       </c>
       <c r="E49" t="n">
         <v>31</v>
       </c>
       <c r="F49" t="n">
-        <v>84.11733661886737</v>
+        <v>85.26920702346727</v>
       </c>
       <c r="G49" t="n">
-        <v>7.670237293050462</v>
+        <v>7.180909410616996</v>
       </c>
       <c r="H49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I49" t="n">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="J49" t="n">
-        <v>0.00140830961640392</v>
+        <v>0.0002517830184661255</v>
       </c>
       <c r="K49" t="n">
-        <v>0.04224928849211759</v>
+        <v>0.007553490553983765</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
@@ -2408,31 +2420,31 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>75.64225578453409</v>
+        <v>75.55793178032317</v>
       </c>
       <c r="D50" t="n">
-        <v>8.36386086089971</v>
+        <v>8.435858009480608</v>
       </c>
       <c r="E50" t="n">
         <v>31</v>
       </c>
       <c r="F50" t="n">
-        <v>86.99556208176053</v>
+        <v>87.10938907242195</v>
       </c>
       <c r="G50" t="n">
-        <v>4.13283136116195</v>
+        <v>4.300151837977963</v>
       </c>
       <c r="H50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I50" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="J50" t="n">
-        <v>2.175921212496173e-06</v>
+        <v>4.354636100083719e-06</v>
       </c>
       <c r="K50" t="n">
-        <v>6.527763637488519e-05</v>
+        <v>0.0001306390830025116</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -2448,31 +2460,31 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>68.52982012264944</v>
+        <v>68.50216713824635</v>
       </c>
       <c r="D51" t="n">
-        <v>9.183066034942964</v>
+        <v>9.146989824822038</v>
       </c>
       <c r="E51" t="n">
         <v>31</v>
       </c>
       <c r="F51" t="n">
-        <v>78.35545129872771</v>
+        <v>77.9186112285777</v>
       </c>
       <c r="G51" t="n">
-        <v>5.301065314540971</v>
+        <v>4.902100053862183</v>
       </c>
       <c r="H51" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I51" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0001012903708403751</v>
+        <v>0.0001971375739483935</v>
       </c>
       <c r="K51" t="n">
-        <v>0.003038711125211254</v>
+        <v>0.005914127218451804</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -2488,28 +2500,28 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>74.21526321553026</v>
+        <v>74.68152961504924</v>
       </c>
       <c r="D52" t="n">
-        <v>7.893433898364248</v>
+        <v>7.907812271215602</v>
       </c>
       <c r="E52" t="n">
         <v>31</v>
       </c>
       <c r="F52" t="n">
-        <v>77.74580444764993</v>
+        <v>78.04118410596635</v>
       </c>
       <c r="G52" t="n">
-        <v>8.722792323556586</v>
+        <v>9.107814412316797</v>
       </c>
       <c r="H52" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I52" t="n">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="J52" t="n">
-        <v>0.349429650644948</v>
+        <v>0.4367377719340795</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
@@ -2528,31 +2540,31 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>74.49127375662204</v>
+        <v>73.65424595881284</v>
       </c>
       <c r="D53" t="n">
-        <v>9.355570629905465</v>
+        <v>9.307861897908412</v>
       </c>
       <c r="E53" t="n">
         <v>31</v>
       </c>
       <c r="F53" t="n">
-        <v>83.96711247258688</v>
+        <v>84.07724769472533</v>
       </c>
       <c r="G53" t="n">
-        <v>3.769631815733116</v>
+        <v>3.771568456893578</v>
       </c>
       <c r="H53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I53" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0005737107869879353</v>
+        <v>0.0002957877326177089</v>
       </c>
       <c r="K53" t="n">
-        <v>0.01721132360963806</v>
+        <v>0.008873631978531266</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -2568,31 +2580,31 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>64.73342088653615</v>
+        <v>65.2265699367986</v>
       </c>
       <c r="D54" t="n">
-        <v>6.908463965700709</v>
+        <v>7.641733417031235</v>
       </c>
       <c r="E54" t="n">
         <v>31</v>
       </c>
       <c r="F54" t="n">
-        <v>75.06743806478887</v>
+        <v>73.42891502973208</v>
       </c>
       <c r="G54" t="n">
-        <v>7.707937397400211</v>
+        <v>6.247842523065091</v>
       </c>
       <c r="H54" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I54" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J54" t="n">
-        <v>3.216398060068791e-05</v>
+        <v>0.0003754792844051885</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0009649194180206372</v>
+        <v>0.01126437853215565</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
@@ -2608,31 +2620,31 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>65.57952191968519</v>
+        <v>64.95100246104131</v>
       </c>
       <c r="D55" t="n">
-        <v>13.80970712726764</v>
+        <v>13.26776599344178</v>
       </c>
       <c r="E55" t="n">
         <v>31</v>
       </c>
       <c r="F55" t="n">
-        <v>75.3248267409146</v>
+        <v>76.42865940939546</v>
       </c>
       <c r="G55" t="n">
-        <v>7.728199629176373</v>
+        <v>7.356198266484053</v>
       </c>
       <c r="H55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I55" t="n">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="J55" t="n">
-        <v>0.02997434472443026</v>
+        <v>0.007237698389998755</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8992303417329076</v>
+        <v>0.2171309516999626</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2648,31 +2660,31 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>58.87282315493466</v>
+        <v>58.22315084804147</v>
       </c>
       <c r="D56" t="n">
-        <v>11.75398721395554</v>
+        <v>11.22812420272703</v>
       </c>
       <c r="E56" t="n">
         <v>31</v>
       </c>
       <c r="F56" t="n">
-        <v>74.31878809262085</v>
+        <v>74.65846712228017</v>
       </c>
       <c r="G56" t="n">
-        <v>3.405992613507525</v>
+        <v>3.370997224723181</v>
       </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I56" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="J56" t="n">
-        <v>6.248188349391799e-05</v>
+        <v>2.223948619916976e-05</v>
       </c>
       <c r="K56" t="n">
-        <v>0.00187445650481754</v>
+        <v>0.0006671845859750929</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -2688,31 +2700,31 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>69.36076912626672</v>
+        <v>69.1238559453388</v>
       </c>
       <c r="D57" t="n">
-        <v>10.63032924642153</v>
+        <v>10.83592956801648</v>
       </c>
       <c r="E57" t="n">
         <v>31</v>
       </c>
       <c r="F57" t="n">
-        <v>79.10234916198752</v>
+        <v>79.58282318913722</v>
       </c>
       <c r="G57" t="n">
-        <v>5.36934965898512</v>
+        <v>5.449413825380664</v>
       </c>
       <c r="H57" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I57" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="J57" t="n">
-        <v>0.002089646376548812</v>
+        <v>0.001678188776517047</v>
       </c>
       <c r="K57" t="n">
-        <v>0.06268939129646436</v>
+        <v>0.05034566329551142</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2728,31 +2740,31 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>71.42866951311549</v>
+        <v>71.82132358912614</v>
       </c>
       <c r="D58" t="n">
-        <v>8.500947420059584</v>
+        <v>9.108199408568948</v>
       </c>
       <c r="E58" t="n">
         <v>31</v>
       </c>
       <c r="F58" t="n">
-        <v>81.42846353704769</v>
+        <v>81.99320546239943</v>
       </c>
       <c r="G58" t="n">
-        <v>5.260913073387782</v>
+        <v>5.229248928226049</v>
       </c>
       <c r="H58" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I58" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J58" t="n">
-        <v>9.353710291066545e-05</v>
+        <v>0.0002321583819918567</v>
       </c>
       <c r="K58" t="n">
-        <v>0.002806113087319963</v>
+        <v>0.0069647514597557</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2768,28 +2780,28 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>76.15310874320933</v>
+        <v>76.75826510334056</v>
       </c>
       <c r="D59" t="n">
-        <v>9.241082727829621</v>
+        <v>8.944289152876637</v>
       </c>
       <c r="E59" t="n">
         <v>31</v>
       </c>
       <c r="F59" t="n">
-        <v>75.74438157810145</v>
+        <v>75.75489365658012</v>
       </c>
       <c r="G59" t="n">
-        <v>5.467342904785914</v>
+        <v>5.540203738084959</v>
       </c>
       <c r="H59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I59" t="n">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="J59" t="n">
-        <v>0.5957310910030567</v>
+        <v>0.4009471464498797</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -2808,31 +2820,31 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>70.74647557954891</v>
+        <v>70.66673877416606</v>
       </c>
       <c r="D60" t="n">
-        <v>10.66605444050738</v>
+        <v>10.63892902729767</v>
       </c>
       <c r="E60" t="n">
         <v>31</v>
       </c>
       <c r="F60" t="n">
-        <v>78.72656621175051</v>
+        <v>78.98664807412023</v>
       </c>
       <c r="G60" t="n">
-        <v>7.304237328729708</v>
+        <v>7.65220205465508</v>
       </c>
       <c r="H60" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I60" t="n">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0131709758686265</v>
+        <v>0.01106840746245952</v>
       </c>
       <c r="K60" t="n">
-        <v>0.395129276058795</v>
+        <v>0.3320522238737856</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2848,31 +2860,31 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>66.01663329574421</v>
+        <v>65.79549786932893</v>
       </c>
       <c r="D61" t="n">
-        <v>9.675239509882399</v>
+        <v>9.395090662529787</v>
       </c>
       <c r="E61" t="n">
         <v>31</v>
       </c>
       <c r="F61" t="n">
-        <v>79.61327935768622</v>
+        <v>80.01394862358435</v>
       </c>
       <c r="G61" t="n">
-        <v>6.838230566586356</v>
+        <v>7.094508162937813</v>
       </c>
       <c r="H61" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I61" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="J61" t="n">
-        <v>1.765717381274922e-05</v>
+        <v>1.531637591240853e-05</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0005297152143824768</v>
+        <v>0.0004594912773722558</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -2888,28 +2900,28 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>93.67440868779764</v>
+        <v>94.32730980865715</v>
       </c>
       <c r="D62" t="n">
-        <v>21.1848351426039</v>
+        <v>21.52058975512291</v>
       </c>
       <c r="E62" t="n">
         <v>31</v>
       </c>
       <c r="F62" t="n">
-        <v>93.83225874640024</v>
+        <v>94.8772112785844</v>
       </c>
       <c r="G62" t="n">
-        <v>12.72436282670548</v>
+        <v>12.95964190040485</v>
       </c>
       <c r="H62" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I62" t="n">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8545777847182893</v>
+        <v>0.9091865156270087</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2928,31 +2940,31 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>107.3949107225795</v>
+        <v>107.8128248091215</v>
       </c>
       <c r="D63" t="n">
-        <v>13.01410019278428</v>
+        <v>13.06087273967087</v>
       </c>
       <c r="E63" t="n">
         <v>31</v>
       </c>
       <c r="F63" t="n">
-        <v>47.83439763188526</v>
+        <v>48.10073788711199</v>
       </c>
       <c r="G63" t="n">
-        <v>8.410643199403561</v>
+        <v>8.798456868704507</v>
       </c>
       <c r="H63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I63" t="n">
-        <v>620</v>
+        <v>558</v>
       </c>
       <c r="J63" t="n">
-        <v>2.356708487617561e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K63" t="n">
-        <v>7.070125462852682e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -2968,31 +2980,31 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>110.2968060642232</v>
+        <v>109.3477943516265</v>
       </c>
       <c r="D64" t="n">
-        <v>8.24590510520196</v>
+        <v>9.245734997519589</v>
       </c>
       <c r="E64" t="n">
         <v>31</v>
       </c>
       <c r="F64" t="n">
-        <v>122.7319235953675</v>
+        <v>126.2069560178089</v>
       </c>
       <c r="G64" t="n">
-        <v>14.92376457749157</v>
+        <v>11.16992373188937</v>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I64" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0007610736202452088</v>
+        <v>1.847133499743414e-05</v>
       </c>
       <c r="K64" t="n">
-        <v>0.02283220860735627</v>
+        <v>0.0005541400499230242</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
@@ -3008,31 +3020,31 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>118.0131750406656</v>
+        <v>118.4908532150342</v>
       </c>
       <c r="D65" t="n">
-        <v>14.03209021309332</v>
+        <v>13.13564246619548</v>
       </c>
       <c r="E65" t="n">
         <v>31</v>
       </c>
       <c r="F65" t="n">
-        <v>36.48927340542853</v>
+        <v>35.8233164157969</v>
       </c>
       <c r="G65" t="n">
-        <v>7.9636230833154</v>
+        <v>8.093253302281974</v>
       </c>
       <c r="H65" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I65" t="n">
-        <v>620</v>
+        <v>558</v>
       </c>
       <c r="J65" t="n">
-        <v>2.356708487617561e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K65" t="n">
-        <v>7.070125462852682e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3048,28 +3060,28 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>106.5983814144053</v>
+        <v>107.3930173079998</v>
       </c>
       <c r="D66" t="n">
-        <v>13.18678490901131</v>
+        <v>13.80907631822212</v>
       </c>
       <c r="E66" t="n">
         <v>31</v>
       </c>
       <c r="F66" t="n">
-        <v>101.367176337234</v>
+        <v>102.8453467414167</v>
       </c>
       <c r="G66" t="n">
-        <v>16.07802915562395</v>
+        <v>16.28813164844694</v>
       </c>
       <c r="H66" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I66" t="n">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1677627224616559</v>
+        <v>0.2412952675894003</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3088,28 +3100,28 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>120.3772721567894</v>
+        <v>121.5339187490483</v>
       </c>
       <c r="D67" t="n">
-        <v>14.13242484032378</v>
+        <v>12.13027829579363</v>
       </c>
       <c r="E67" t="n">
         <v>31</v>
       </c>
       <c r="F67" t="n">
-        <v>114.3353077323688</v>
+        <v>118.5180582786997</v>
       </c>
       <c r="G67" t="n">
-        <v>17.37547070838898</v>
+        <v>12.34766583841179</v>
       </c>
       <c r="H67" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I67" t="n">
-        <v>366</v>
+        <v>312</v>
       </c>
       <c r="J67" t="n">
-        <v>0.2842840647964374</v>
+        <v>0.5002994875609216</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -3128,28 +3140,28 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>94.43289898626524</v>
+        <v>93.60315074977595</v>
       </c>
       <c r="D68" t="n">
-        <v>19.66305061977191</v>
+        <v>19.14211251540715</v>
       </c>
       <c r="E68" t="n">
         <v>31</v>
       </c>
       <c r="F68" t="n">
-        <v>91.30845337295493</v>
+        <v>92.6292051310852</v>
       </c>
       <c r="G68" t="n">
-        <v>12.89985057647105</v>
+        <v>12.93371327313418</v>
       </c>
       <c r="H68" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I68" t="n">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="J68" t="n">
-        <v>0.7067624672048755</v>
+        <v>0.9751829703855429</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3168,31 +3180,31 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>76.36550599761628</v>
+        <v>76.58596089344611</v>
       </c>
       <c r="D69" t="n">
-        <v>15.99487854972812</v>
+        <v>15.91055606462162</v>
       </c>
       <c r="E69" t="n">
         <v>31</v>
       </c>
       <c r="F69" t="n">
-        <v>52.74711284541386</v>
+        <v>54.10155823444911</v>
       </c>
       <c r="G69" t="n">
-        <v>20.81779968609993</v>
+        <v>21.50221223883493</v>
       </c>
       <c r="H69" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I69" t="n">
-        <v>504</v>
+        <v>443</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0001891087115364504</v>
+        <v>0.0006968078999980682</v>
       </c>
       <c r="K69" t="n">
-        <v>0.005673261346093513</v>
+        <v>0.02090423699994205</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
@@ -3208,31 +3220,31 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>102.8521478364503</v>
+        <v>102.6051469411067</v>
       </c>
       <c r="D70" t="n">
-        <v>16.38437768078824</v>
+        <v>16.43511488195872</v>
       </c>
       <c r="E70" t="n">
         <v>31</v>
       </c>
       <c r="F70" t="n">
-        <v>48.18147876968318</v>
+        <v>47.08473643363352</v>
       </c>
       <c r="G70" t="n">
-        <v>12.55182005655211</v>
+        <v>12.74344670794645</v>
       </c>
       <c r="H70" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I70" t="n">
-        <v>619</v>
+        <v>557</v>
       </c>
       <c r="J70" t="n">
-        <v>2.652105483629477e-09</v>
+        <v>8.659979663152756e-09</v>
       </c>
       <c r="K70" t="n">
-        <v>7.956316450888431e-08</v>
+        <v>2.597993898945827e-07</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
@@ -3248,31 +3260,31 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>112.9352867174881</v>
+        <v>112.6999849787822</v>
       </c>
       <c r="D71" t="n">
-        <v>15.89086818427197</v>
+        <v>15.84817850929677</v>
       </c>
       <c r="E71" t="n">
         <v>31</v>
       </c>
       <c r="F71" t="n">
-        <v>81.22901323448303</v>
+        <v>83.62939336846175</v>
       </c>
       <c r="G71" t="n">
-        <v>25.45845339380993</v>
+        <v>25.72178668245885</v>
       </c>
       <c r="H71" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I71" t="n">
-        <v>518</v>
+        <v>454</v>
       </c>
       <c r="J71" t="n">
-        <v>6.248188349391799e-05</v>
+        <v>0.0002957877326177089</v>
       </c>
       <c r="K71" t="n">
-        <v>0.00187445650481754</v>
+        <v>0.008873631978531266</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
@@ -3288,31 +3300,31 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>120.234979721356</v>
+        <v>121.6460626127822</v>
       </c>
       <c r="D72" t="n">
-        <v>12.82921114795034</v>
+        <v>11.64017300598562</v>
       </c>
       <c r="E72" t="n">
         <v>31</v>
       </c>
       <c r="F72" t="n">
-        <v>66.15430901905516</v>
+        <v>63.47237386734197</v>
       </c>
       <c r="G72" t="n">
-        <v>13.91008370606422</v>
+        <v>11.88954945171794</v>
       </c>
       <c r="H72" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I72" t="n">
-        <v>618</v>
+        <v>558</v>
       </c>
       <c r="J72" t="n">
-        <v>2.983444789227621e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K72" t="n">
-        <v>8.950334367682862e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
@@ -3328,31 +3340,31 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>53.075487053094</v>
+        <v>55.64037599490852</v>
       </c>
       <c r="D73" t="n">
-        <v>27.1833710806999</v>
+        <v>27.17845523526683</v>
       </c>
       <c r="E73" t="n">
         <v>31</v>
       </c>
       <c r="F73" t="n">
-        <v>107.8334555174312</v>
+        <v>107.6952614729486</v>
       </c>
       <c r="G73" t="n">
-        <v>9.211795273706604</v>
+        <v>9.700229479819013</v>
       </c>
       <c r="H73" t="n">
+        <v>18</v>
+      </c>
+      <c r="I73" t="n">
         <v>20</v>
       </c>
-      <c r="I73" t="n">
-        <v>19</v>
-      </c>
       <c r="J73" t="n">
-        <v>2.088201218728604e-08</v>
+        <v>8.274407170209708e-08</v>
       </c>
       <c r="K73" t="n">
-        <v>6.264603656185811e-07</v>
+        <v>2.482322151062912e-06</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -3368,31 +3380,31 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>124.778543673201</v>
+        <v>124.8330257277874</v>
       </c>
       <c r="D74" t="n">
-        <v>6.997162346716442</v>
+        <v>6.818423435211463</v>
       </c>
       <c r="E74" t="n">
         <v>31</v>
       </c>
       <c r="F74" t="n">
-        <v>92.64828901415335</v>
+        <v>93.64849503706859</v>
       </c>
       <c r="G74" t="n">
-        <v>11.34688320597249</v>
+        <v>11.49187843513777</v>
       </c>
       <c r="H74" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I74" t="n">
-        <v>613</v>
+        <v>552</v>
       </c>
       <c r="J74" t="n">
-        <v>5.345509575019857e-09</v>
+        <v>1.591585466085861e-08</v>
       </c>
       <c r="K74" t="n">
-        <v>1.603652872505957e-07</v>
+        <v>4.774756398257584e-07</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
@@ -3408,31 +3420,31 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>89.21244161984048</v>
+        <v>89.40591875497805</v>
       </c>
       <c r="D75" t="n">
-        <v>18.14401679737439</v>
+        <v>18.38879513883349</v>
       </c>
       <c r="E75" t="n">
         <v>31</v>
       </c>
       <c r="F75" t="n">
-        <v>65.48278636419332</v>
+        <v>64.76369571581259</v>
       </c>
       <c r="G75" t="n">
-        <v>12.81920727761852</v>
+        <v>12.78800979423706</v>
       </c>
       <c r="H75" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I75" t="n">
-        <v>521</v>
+        <v>473</v>
       </c>
       <c r="J75" t="n">
-        <v>4.883906414044003e-05</v>
+        <v>5.995113621836463e-05</v>
       </c>
       <c r="K75" t="n">
-        <v>0.001465171924213201</v>
+        <v>0.001798534086550939</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -3448,31 +3460,31 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>89.02925317866728</v>
+        <v>89.0429898349838</v>
       </c>
       <c r="D76" t="n">
-        <v>18.16588164060556</v>
+        <v>18.18506653512703</v>
       </c>
       <c r="E76" t="n">
         <v>31</v>
       </c>
       <c r="F76" t="n">
-        <v>100.8593947981125</v>
+        <v>99.92816982551422</v>
       </c>
       <c r="G76" t="n">
-        <v>7.871840971930786</v>
+        <v>7.75749953532977</v>
       </c>
       <c r="H76" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I76" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="J76" t="n">
-        <v>0.01466584611022816</v>
+        <v>0.03021739396823381</v>
       </c>
       <c r="K76" t="n">
-        <v>0.4399753833068449</v>
+        <v>0.9065218190470142</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -3488,31 +3500,31 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>72.3940085601174</v>
+        <v>72.96485835584861</v>
       </c>
       <c r="D77" t="n">
-        <v>17.77971379766533</v>
+        <v>18.29461236333577</v>
       </c>
       <c r="E77" t="n">
         <v>31</v>
       </c>
       <c r="F77" t="n">
-        <v>97.54840190552025</v>
+        <v>100.2301938028032</v>
       </c>
       <c r="G77" t="n">
-        <v>15.09718700428521</v>
+        <v>11.85039996787323</v>
       </c>
       <c r="H77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I77" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="J77" t="n">
-        <v>7.272481479396425e-06</v>
+        <v>5.308330333267513e-06</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0002181744443818927</v>
+        <v>0.0001592499099980254</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
@@ -3528,31 +3540,31 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>95.25281435356362</v>
+        <v>95.4320453957001</v>
       </c>
       <c r="D78" t="n">
-        <v>17.57392416827326</v>
+        <v>17.3168589255352</v>
       </c>
       <c r="E78" t="n">
         <v>31</v>
       </c>
       <c r="F78" t="n">
-        <v>74.30998529501863</v>
+        <v>74.37944221486968</v>
       </c>
       <c r="G78" t="n">
-        <v>14.6513276355814</v>
+        <v>15.40376255260403</v>
       </c>
       <c r="H78" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I78" t="n">
-        <v>500</v>
+        <v>451</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0002562138635334837</v>
+        <v>0.0003754792844051885</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00768641590600451</v>
+        <v>0.01126437853215565</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -3568,28 +3580,28 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>107.8068757152368</v>
+        <v>107.6235147277104</v>
       </c>
       <c r="D79" t="n">
-        <v>11.06457199126808</v>
+        <v>10.91099094590225</v>
       </c>
       <c r="E79" t="n">
         <v>31</v>
       </c>
       <c r="F79" t="n">
-        <v>96.65288447399024</v>
+        <v>102.6873126987041</v>
       </c>
       <c r="G79" t="n">
-        <v>40.5047851001363</v>
+        <v>38.17899041125145</v>
       </c>
       <c r="H79" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I79" t="n">
-        <v>273</v>
+        <v>210</v>
       </c>
       <c r="J79" t="n">
-        <v>0.4813183777340264</v>
+        <v>0.1554261493299774</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
@@ -3608,31 +3620,31 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>85.57896688612124</v>
+        <v>84.63560478188585</v>
       </c>
       <c r="D80" t="n">
-        <v>16.39281900772366</v>
+        <v>16.00461570726701</v>
       </c>
       <c r="E80" t="n">
         <v>31</v>
       </c>
       <c r="F80" t="n">
-        <v>112.7916710832666</v>
+        <v>112.7557194548261</v>
       </c>
       <c r="G80" t="n">
-        <v>14.28056940026551</v>
+        <v>14.99539470766413</v>
       </c>
       <c r="H80" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I80" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="J80" t="n">
-        <v>1.482907495397085e-05</v>
+        <v>1.682351175484981e-05</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0004448722486191254</v>
+        <v>0.0005047053526454941</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
@@ -3648,31 +3660,31 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>94.67245933894766</v>
+        <v>95.1728476176545</v>
       </c>
       <c r="D81" t="n">
-        <v>20.12724797831465</v>
+        <v>20.94279578899729</v>
       </c>
       <c r="E81" t="n">
         <v>31</v>
       </c>
       <c r="F81" t="n">
-        <v>51.96790630169716</v>
+        <v>51.72669617874717</v>
       </c>
       <c r="G81" t="n">
-        <v>7.129026409568474</v>
+        <v>7.43470423796207</v>
       </c>
       <c r="H81" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I81" t="n">
-        <v>620</v>
+        <v>558</v>
       </c>
       <c r="J81" t="n">
-        <v>2.356708487617561e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K81" t="n">
-        <v>7.070125462852682e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -3688,31 +3700,31 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>112.0040422392677</v>
+        <v>112.5902787522897</v>
       </c>
       <c r="D82" t="n">
-        <v>11.30452721263722</v>
+        <v>11.22133643844153</v>
       </c>
       <c r="E82" t="n">
         <v>31</v>
       </c>
       <c r="F82" t="n">
-        <v>57.74405275412024</v>
+        <v>60.29013081306269</v>
       </c>
       <c r="G82" t="n">
-        <v>40.26296170572795</v>
+        <v>41.6502484137641</v>
       </c>
       <c r="H82" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I82" t="n">
-        <v>499</v>
+        <v>441</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0002761803027780101</v>
+        <v>0.0008100024006653984</v>
       </c>
       <c r="K82" t="n">
-        <v>0.008285409083340304</v>
+        <v>0.02430007201996195</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -3728,28 +3740,28 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>101.3965816847873</v>
+        <v>99.61940350943044</v>
       </c>
       <c r="D83" t="n">
-        <v>22.15287683017908</v>
+        <v>21.78623015910361</v>
       </c>
       <c r="E83" t="n">
         <v>31</v>
       </c>
       <c r="F83" t="n">
-        <v>104.9024365847678</v>
+        <v>104.9265820619649</v>
       </c>
       <c r="G83" t="n">
-        <v>12.46830944494979</v>
+        <v>13.06944995863802</v>
       </c>
       <c r="H83" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I83" t="n">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="J83" t="n">
-        <v>0.6364477383728195</v>
+        <v>0.3894198719045028</v>
       </c>
       <c r="K83" t="n">
         <v>1</v>
@@ -3768,31 +3780,31 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>77.18213740065733</v>
+        <v>79.87724656142585</v>
       </c>
       <c r="D84" t="n">
-        <v>20.04556691662386</v>
+        <v>21.20283449944574</v>
       </c>
       <c r="E84" t="n">
         <v>31</v>
       </c>
       <c r="F84" t="n">
-        <v>64.13054462042763</v>
+        <v>61.50150317586746</v>
       </c>
       <c r="G84" t="n">
-        <v>13.1551614030529</v>
+        <v>11.08609829249928</v>
       </c>
       <c r="H84" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I84" t="n">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="J84" t="n">
-        <v>0.02224341149606007</v>
+        <v>0.003123526642464107</v>
       </c>
       <c r="K84" t="n">
-        <v>0.6673023448818022</v>
+        <v>0.09370579927392322</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3808,31 +3820,31 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>70.72898763911911</v>
+        <v>69.60421508209286</v>
       </c>
       <c r="D85" t="n">
-        <v>20.96381581497512</v>
+        <v>19.35613453925188</v>
       </c>
       <c r="E85" t="n">
         <v>31</v>
       </c>
       <c r="F85" t="n">
-        <v>51.3295756234299</v>
+        <v>53.16700850642318</v>
       </c>
       <c r="G85" t="n">
-        <v>16.30454029094888</v>
+        <v>16.16537364233837</v>
       </c>
       <c r="H85" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I85" t="n">
-        <v>473</v>
+        <v>413</v>
       </c>
       <c r="J85" t="n">
-        <v>0.001718163657837091</v>
+        <v>0.0056287163449574</v>
       </c>
       <c r="K85" t="n">
-        <v>0.05154490973511272</v>
+        <v>0.168861490348722</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3848,28 +3860,28 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>55.09779820575501</v>
+        <v>54.41456860446951</v>
       </c>
       <c r="D86" t="n">
-        <v>21.31923393172334</v>
+        <v>20.05851026768579</v>
       </c>
       <c r="E86" t="n">
         <v>31</v>
       </c>
       <c r="F86" t="n">
-        <v>56.7365166043747</v>
+        <v>52.64884819489543</v>
       </c>
       <c r="G86" t="n">
-        <v>20.94738133977904</v>
+        <v>17.81492029732669</v>
       </c>
       <c r="H86" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I86" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="J86" t="n">
-        <v>0.8697406015562692</v>
+        <v>0.79545167210406</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3888,31 +3900,31 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>89.73391874904874</v>
+        <v>88.47406527509573</v>
       </c>
       <c r="D87" t="n">
-        <v>15.24380987802058</v>
+        <v>14.74903890801164</v>
       </c>
       <c r="E87" t="n">
         <v>31</v>
       </c>
       <c r="F87" t="n">
-        <v>66.33070760063717</v>
+        <v>63.80306549503362</v>
       </c>
       <c r="G87" t="n">
-        <v>11.99379861364357</v>
+        <v>9.703395213597283</v>
       </c>
       <c r="H87" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I87" t="n">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="J87" t="n">
-        <v>5.534570459384453e-06</v>
+        <v>1.93969044836985e-06</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0001660371137815336</v>
+        <v>5.819071345109551e-05</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -3928,28 +3940,28 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>104.9834723619477</v>
+        <v>105.2325350182129</v>
       </c>
       <c r="D88" t="n">
-        <v>18.95520153131339</v>
+        <v>19.15159536078909</v>
       </c>
       <c r="E88" t="n">
         <v>31</v>
       </c>
       <c r="F88" t="n">
-        <v>100.0603513877823</v>
+        <v>104.6281768035724</v>
       </c>
       <c r="G88" t="n">
-        <v>33.1857063125437</v>
+        <v>31.84832741076281</v>
       </c>
       <c r="H88" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I88" t="n">
-        <v>311</v>
+        <v>251</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9923034439407639</v>
+        <v>0.5684583509373714</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -3968,31 +3980,31 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>120.441984451063</v>
+        <v>121.6561773768601</v>
       </c>
       <c r="D89" t="n">
-        <v>9.722696918323116</v>
+        <v>9.347919341091787</v>
       </c>
       <c r="E89" t="n">
         <v>31</v>
       </c>
       <c r="F89" t="n">
-        <v>65.94229849580287</v>
+        <v>62.38517690228673</v>
       </c>
       <c r="G89" t="n">
-        <v>14.79272485545779</v>
+        <v>10.69143275276227</v>
       </c>
       <c r="H89" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I89" t="n">
-        <v>618</v>
+        <v>558</v>
       </c>
       <c r="J89" t="n">
-        <v>2.983444789227621e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K89" t="n">
-        <v>8.950334367682862e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -4008,28 +4020,28 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>106.314898923018</v>
+        <v>107.2327149269393</v>
       </c>
       <c r="D90" t="n">
-        <v>20.28363377041078</v>
+        <v>19.91130263072061</v>
       </c>
       <c r="E90" t="n">
         <v>31</v>
       </c>
       <c r="F90" t="n">
-        <v>88.0670392439186</v>
+        <v>92.96812635731712</v>
       </c>
       <c r="G90" t="n">
-        <v>31.07600850074737</v>
+        <v>28.85179183440063</v>
       </c>
       <c r="H90" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I90" t="n">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="J90" t="n">
-        <v>0.07433025648395089</v>
+        <v>0.1494821982593604</v>
       </c>
       <c r="K90" t="n">
         <v>1</v>
@@ -4048,31 +4060,31 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>73.28760146733565</v>
+        <v>73.43728869001139</v>
       </c>
       <c r="D91" t="n">
-        <v>15.82301506008063</v>
+        <v>16.10530617443236</v>
       </c>
       <c r="E91" t="n">
         <v>31</v>
       </c>
       <c r="F91" t="n">
-        <v>91.7868558145945</v>
+        <v>92.63687512339229</v>
       </c>
       <c r="G91" t="n">
-        <v>12.58596721183036</v>
+        <v>12.05227326082204</v>
       </c>
       <c r="H91" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I91" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0001891087115364504</v>
+        <v>0.0001815500411740529</v>
       </c>
       <c r="K91" t="n">
-        <v>0.005673261346093513</v>
+        <v>0.005446501235221588</v>
       </c>
       <c r="L91" t="b">
         <v>1</v>
@@ -4088,28 +4100,28 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>10.37892196078356</v>
+        <v>10.13920844080832</v>
       </c>
       <c r="D92" t="n">
-        <v>4.653245107537068</v>
+        <v>4.800554597979963</v>
       </c>
       <c r="E92" t="n">
         <v>31</v>
       </c>
       <c r="F92" t="n">
-        <v>12.02105286306107</v>
+        <v>11.57671071133554</v>
       </c>
       <c r="G92" t="n">
-        <v>1.989488285300599</v>
+        <v>1.545049120509512</v>
       </c>
       <c r="H92" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I92" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="J92" t="n">
-        <v>0.3800424713883037</v>
+        <v>0.6113787759905555</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4128,31 +4140,31 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>8.517997221057694</v>
+        <v>8.30452649056933</v>
       </c>
       <c r="D93" t="n">
-        <v>2.797806296429114</v>
+        <v>2.460709557142981</v>
       </c>
       <c r="E93" t="n">
         <v>31</v>
       </c>
       <c r="F93" t="n">
-        <v>17.18404723057711</v>
+        <v>16.72095747498246</v>
       </c>
       <c r="G93" t="n">
-        <v>2.512915244573704</v>
+        <v>2.204872343755658</v>
       </c>
       <c r="H93" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I93" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>6.732778635407067e-09</v>
+        <v>1.106083286268991e-08</v>
       </c>
       <c r="K93" t="n">
-        <v>2.01983359062212e-07</v>
+        <v>3.318249858806974e-07</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -4168,31 +4180,31 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>10.42843555435136</v>
+        <v>10.46870001153313</v>
       </c>
       <c r="D94" t="n">
-        <v>3.054742060539623</v>
+        <v>3.069749375733672</v>
       </c>
       <c r="E94" t="n">
         <v>31</v>
       </c>
       <c r="F94" t="n">
-        <v>14.27579642188293</v>
+        <v>13.83589806039506</v>
       </c>
       <c r="G94" t="n">
-        <v>3.058728069126974</v>
+        <v>2.906881122495357</v>
       </c>
       <c r="H94" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I94" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0002041333948081417</v>
+        <v>0.001089251025978756</v>
       </c>
       <c r="K94" t="n">
-        <v>0.00612400184424425</v>
+        <v>0.03267753077936267</v>
       </c>
       <c r="L94" t="b">
         <v>1</v>
@@ -4208,31 +4220,31 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>10.67666246835243</v>
+        <v>10.52104133447807</v>
       </c>
       <c r="D95" t="n">
-        <v>3.361068683133005</v>
+        <v>3.275197246933631</v>
       </c>
       <c r="E95" t="n">
         <v>31</v>
       </c>
       <c r="F95" t="n">
-        <v>19.11330628227677</v>
+        <v>19.24700042247565</v>
       </c>
       <c r="G95" t="n">
-        <v>1.099162239399411</v>
+        <v>1.040661653123909</v>
       </c>
       <c r="H95" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>2.356708487617561e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K95" t="n">
-        <v>7.070125462852682e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -4248,31 +4260,31 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>12.62832310604462</v>
+        <v>12.22048385266111</v>
       </c>
       <c r="D96" t="n">
-        <v>3.931045597660516</v>
+        <v>4.019372800283999</v>
       </c>
       <c r="E96" t="n">
         <v>31</v>
       </c>
       <c r="F96" t="n">
-        <v>15.65041434935584</v>
+        <v>15.82652627231393</v>
       </c>
       <c r="G96" t="n">
-        <v>2.357443609359832</v>
+        <v>2.419342523936659</v>
       </c>
       <c r="H96" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I96" t="n">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="J96" t="n">
-        <v>0.005306798846624329</v>
+        <v>0.001932036292444059</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1592039653987299</v>
+        <v>0.05796108877332178</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4288,34 +4300,34 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>9.229248321742185</v>
+        <v>8.956298432405598</v>
       </c>
       <c r="D97" t="n">
-        <v>4.447960200987837</v>
+        <v>4.106361893332288</v>
       </c>
       <c r="E97" t="n">
         <v>31</v>
       </c>
       <c r="F97" t="n">
-        <v>12.09486997048971</v>
+        <v>11.62831280858063</v>
       </c>
       <c r="G97" t="n">
-        <v>1.838895377085381</v>
+        <v>1.207729073788496</v>
       </c>
       <c r="H97" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I97" t="n">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="J97" t="n">
-        <v>0.001718163657837091</v>
+        <v>0.001260079759530211</v>
       </c>
       <c r="K97" t="n">
-        <v>0.05154490973511272</v>
+        <v>0.03780239278590632</v>
       </c>
       <c r="L97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4328,31 +4340,31 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>10.2040988940981</v>
+        <v>10.1621500464072</v>
       </c>
       <c r="D98" t="n">
-        <v>2.23678622560584</v>
+        <v>2.214842844504965</v>
       </c>
       <c r="E98" t="n">
         <v>31</v>
       </c>
       <c r="F98" t="n">
-        <v>16.42564631689456</v>
+        <v>16.25898754011938</v>
       </c>
       <c r="G98" t="n">
-        <v>2.070786843742486</v>
+        <v>2.088491846515291</v>
       </c>
       <c r="H98" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I98" t="n">
         <v>9</v>
       </c>
       <c r="J98" t="n">
-        <v>6.732778635407067e-09</v>
+        <v>2.281579882117859e-08</v>
       </c>
       <c r="K98" t="n">
-        <v>2.01983359062212e-07</v>
+        <v>6.844739646353578e-07</v>
       </c>
       <c r="L98" t="b">
         <v>1</v>
@@ -4368,31 +4380,31 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>10.77268540469488</v>
+        <v>10.57537047987094</v>
       </c>
       <c r="D99" t="n">
-        <v>4.506478325536457</v>
+        <v>4.391881460088997</v>
       </c>
       <c r="E99" t="n">
         <v>31</v>
       </c>
       <c r="F99" t="n">
-        <v>16.35882498155606</v>
+        <v>16.49913132373615</v>
       </c>
       <c r="G99" t="n">
-        <v>1.918374093901219</v>
+        <v>1.96431649434585</v>
       </c>
       <c r="H99" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I99" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="J99" t="n">
-        <v>4.198421074370363e-06</v>
+        <v>2.635054954307537e-06</v>
       </c>
       <c r="K99" t="n">
-        <v>0.0001259526322311109</v>
+        <v>7.905164862922612e-05</v>
       </c>
       <c r="L99" t="b">
         <v>1</v>
@@ -4408,31 +4420,31 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>11.50459683368998</v>
+        <v>11.3309923002429</v>
       </c>
       <c r="D100" t="n">
-        <v>3.69819731602353</v>
+        <v>3.618135521157929</v>
       </c>
       <c r="E100" t="n">
         <v>31</v>
       </c>
       <c r="F100" t="n">
-        <v>17.22234492934561</v>
+        <v>16.86312393986968</v>
       </c>
       <c r="G100" t="n">
-        <v>2.483521209666942</v>
+        <v>2.350942447732943</v>
       </c>
       <c r="H100" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I100" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J100" t="n">
-        <v>3.174590564650748e-06</v>
+        <v>7.122289332759604e-06</v>
       </c>
       <c r="K100" t="n">
-        <v>9.523771693952245e-05</v>
+        <v>0.0002136686799827881</v>
       </c>
       <c r="L100" t="b">
         <v>1</v>
@@ -4448,31 +4460,31 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>11.80882218064585</v>
+        <v>11.61932435821624</v>
       </c>
       <c r="D101" t="n">
-        <v>3.227926748515529</v>
+        <v>3.232843154268437</v>
       </c>
       <c r="E101" t="n">
         <v>31</v>
       </c>
       <c r="F101" t="n">
-        <v>17.32311900573176</v>
+        <v>16.92918542584917</v>
       </c>
       <c r="G101" t="n">
-        <v>3.51061719295953</v>
+        <v>3.483162279857276</v>
       </c>
       <c r="H101" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I101" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="J101" t="n">
-        <v>1.04145295263826e-05</v>
+        <v>2.438763609416404e-05</v>
       </c>
       <c r="K101" t="n">
-        <v>0.000312435885791478</v>
+        <v>0.0007316290828249213</v>
       </c>
       <c r="L101" t="b">
         <v>1</v>
@@ -4488,31 +4500,31 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>10.17129657428542</v>
+        <v>9.92943797814555</v>
       </c>
       <c r="D102" t="n">
-        <v>3.955971733874967</v>
+        <v>3.750128784732035</v>
       </c>
       <c r="E102" t="n">
         <v>31</v>
       </c>
       <c r="F102" t="n">
-        <v>18.99775218489298</v>
+        <v>18.96649042493484</v>
       </c>
       <c r="G102" t="n">
-        <v>1.322104473930219</v>
+        <v>1.363076531445254</v>
       </c>
       <c r="H102" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>2.983444789227621e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K102" t="n">
-        <v>8.950334367682862e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -4528,28 +4540,28 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>14.47541482761583</v>
+        <v>14.25417147977757</v>
       </c>
       <c r="D103" t="n">
-        <v>2.902051233015092</v>
+        <v>2.988104895228664</v>
       </c>
       <c r="E103" t="n">
         <v>31</v>
       </c>
       <c r="F103" t="n">
-        <v>13.57172833550871</v>
+        <v>13.57009376438461</v>
       </c>
       <c r="G103" t="n">
-        <v>1.809206755748899</v>
+        <v>1.837954725444613</v>
       </c>
       <c r="H103" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I103" t="n">
-        <v>391</v>
+        <v>334</v>
       </c>
       <c r="J103" t="n">
-        <v>0.1204081582509096</v>
+        <v>0.2583593766733072</v>
       </c>
       <c r="K103" t="n">
         <v>1</v>
@@ -4568,31 +4580,31 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>9.723229202326372</v>
+        <v>9.53844642847333</v>
       </c>
       <c r="D104" t="n">
-        <v>3.079561727106487</v>
+        <v>2.916421215217815</v>
       </c>
       <c r="E104" t="n">
         <v>31</v>
       </c>
       <c r="F104" t="n">
-        <v>14.77805785710228</v>
+        <v>14.24344130109903</v>
       </c>
       <c r="G104" t="n">
-        <v>4.424944051123724</v>
+        <v>4.32852996777517</v>
       </c>
       <c r="H104" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I104" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0004624285698355455</v>
+        <v>0.001012116276347626</v>
       </c>
       <c r="K104" t="n">
-        <v>0.01387285709506637</v>
+        <v>0.03036348829042879</v>
       </c>
       <c r="L104" t="b">
         <v>1</v>
@@ -4608,31 +4620,31 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>13.6985842588846</v>
+        <v>13.52997504810055</v>
       </c>
       <c r="D105" t="n">
-        <v>1.717805498900318</v>
+        <v>2.052216952454703</v>
       </c>
       <c r="E105" t="n">
         <v>31</v>
       </c>
       <c r="F105" t="n">
-        <v>16.78375815787975</v>
+        <v>16.70275964915594</v>
       </c>
       <c r="G105" t="n">
-        <v>1.515797316046525</v>
+        <v>1.506881623950601</v>
       </c>
       <c r="H105" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I105" t="n">
         <v>53</v>
       </c>
       <c r="J105" t="n">
-        <v>7.475738716492907e-07</v>
+        <v>2.915962765362787e-06</v>
       </c>
       <c r="K105" t="n">
-        <v>2.242721614947872e-05</v>
+        <v>8.747888296088361e-05</v>
       </c>
       <c r="L105" t="b">
         <v>1</v>
@@ -4648,31 +4660,31 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>11.36392551226447</v>
+        <v>11.18262932241769</v>
       </c>
       <c r="D106" t="n">
-        <v>3.169347094969573</v>
+        <v>3.348914013897093</v>
       </c>
       <c r="E106" t="n">
         <v>31</v>
       </c>
       <c r="F106" t="n">
-        <v>14.69345049940407</v>
+        <v>14.55150057696304</v>
       </c>
       <c r="G106" t="n">
-        <v>1.223881961583311</v>
+        <v>1.195422489938295</v>
       </c>
       <c r="H106" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I106" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J106" t="n">
-        <v>0.0002202740668781602</v>
+        <v>0.0005131659755255744</v>
       </c>
       <c r="K106" t="n">
-        <v>0.006608222006344806</v>
+        <v>0.01539497926576723</v>
       </c>
       <c r="L106" t="b">
         <v>1</v>
@@ -4688,31 +4700,31 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>13.3450758900212</v>
+        <v>13.39393589210816</v>
       </c>
       <c r="D107" t="n">
-        <v>2.689150543765268</v>
+        <v>2.652481807052144</v>
       </c>
       <c r="E107" t="n">
         <v>31</v>
       </c>
       <c r="F107" t="n">
-        <v>17.4221306963282</v>
+        <v>16.92000682582017</v>
       </c>
       <c r="G107" t="n">
-        <v>2.915181187882395</v>
+        <v>2.624147227455401</v>
       </c>
       <c r="H107" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I107" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J107" t="n">
-        <v>4.495692433815382e-05</v>
+        <v>0.0001971375739483935</v>
       </c>
       <c r="K107" t="n">
-        <v>0.001348707730144615</v>
+        <v>0.005914127218451804</v>
       </c>
       <c r="L107" t="b">
         <v>1</v>
@@ -4728,31 +4740,31 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>10.8973176250478</v>
+        <v>10.56756591749944</v>
       </c>
       <c r="D108" t="n">
-        <v>4.5739559092244</v>
+        <v>4.424920493646126</v>
       </c>
       <c r="E108" t="n">
         <v>31</v>
       </c>
       <c r="F108" t="n">
-        <v>16.53493800011346</v>
+        <v>16.29266342558433</v>
       </c>
       <c r="G108" t="n">
-        <v>2.712130245872533</v>
+        <v>2.748810288887749</v>
       </c>
       <c r="H108" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I108" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="J108" t="n">
-        <v>7.968083572110736e-05</v>
+        <v>6.544544663072697e-05</v>
       </c>
       <c r="K108" t="n">
-        <v>0.002390425071633221</v>
+        <v>0.001963363398921809</v>
       </c>
       <c r="L108" t="b">
         <v>1</v>
@@ -4768,31 +4780,31 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>10.4273918034017</v>
+        <v>10.05135212567113</v>
       </c>
       <c r="D109" t="n">
-        <v>4.732362615603086</v>
+        <v>4.921373471818723</v>
       </c>
       <c r="E109" t="n">
         <v>31</v>
       </c>
       <c r="F109" t="n">
-        <v>15.41832366210765</v>
+        <v>14.96498503994597</v>
       </c>
       <c r="G109" t="n">
-        <v>3.650316691190347</v>
+        <v>3.562226285211444</v>
       </c>
       <c r="H109" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I109" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="J109" t="n">
-        <v>0.002089646376548812</v>
+        <v>0.004349745332208783</v>
       </c>
       <c r="K109" t="n">
-        <v>0.06268939129646436</v>
+        <v>0.1304923599662635</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4808,31 +4820,31 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>12.49271671813869</v>
+        <v>12.54138559929406</v>
       </c>
       <c r="D110" t="n">
-        <v>2.634300272277581</v>
+        <v>2.624314263513365</v>
       </c>
       <c r="E110" t="n">
         <v>31</v>
       </c>
       <c r="F110" t="n">
-        <v>17.45736833891374</v>
+        <v>17.59060850689512</v>
       </c>
       <c r="G110" t="n">
-        <v>2.251481388234119</v>
+        <v>2.307895377717411</v>
       </c>
       <c r="H110" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I110" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J110" t="n">
-        <v>5.014702446342466e-07</v>
+        <v>1.422504478890153e-06</v>
       </c>
       <c r="K110" t="n">
-        <v>1.50441073390274e-05</v>
+        <v>4.267513436670458e-05</v>
       </c>
       <c r="L110" t="b">
         <v>1</v>
@@ -4848,31 +4860,31 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>11.49464426609741</v>
+        <v>11.08233454034863</v>
       </c>
       <c r="D111" t="n">
-        <v>3.483152212339426</v>
+        <v>3.567719984578188</v>
       </c>
       <c r="E111" t="n">
         <v>31</v>
       </c>
       <c r="F111" t="n">
-        <v>15.40941745644396</v>
+        <v>15.20701459432868</v>
       </c>
       <c r="G111" t="n">
-        <v>1.496551594019673</v>
+        <v>1.440216107576344</v>
       </c>
       <c r="H111" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I111" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="J111" t="n">
-        <v>7.272481479396425e-06</v>
+        <v>7.122289332759604e-06</v>
       </c>
       <c r="K111" t="n">
-        <v>0.0002181744443818927</v>
+        <v>0.0002136686799827881</v>
       </c>
       <c r="L111" t="b">
         <v>1</v>
@@ -4888,31 +4900,31 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>10.52972635290367</v>
+        <v>10.45589998919908</v>
       </c>
       <c r="D112" t="n">
-        <v>2.531681715946775</v>
+        <v>2.53962448328391</v>
       </c>
       <c r="E112" t="n">
         <v>31</v>
       </c>
       <c r="F112" t="n">
-        <v>19.1681922847738</v>
+        <v>18.93856801228328</v>
       </c>
       <c r="G112" t="n">
-        <v>3.223408508872413</v>
+        <v>3.308582814354978</v>
       </c>
       <c r="H112" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I112" t="n">
         <v>8</v>
       </c>
       <c r="J112" t="n">
-        <v>6.000265975999325e-09</v>
+        <v>2.024334202803621e-08</v>
       </c>
       <c r="K112" t="n">
-        <v>1.800079792799798e-07</v>
+        <v>6.073002608410862e-07</v>
       </c>
       <c r="L112" t="b">
         <v>1</v>
@@ -4928,31 +4940,31 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>9.411361077599834</v>
+        <v>9.503915324640111</v>
       </c>
       <c r="D113" t="n">
-        <v>2.733082320726707</v>
+        <v>2.857597870106401</v>
       </c>
       <c r="E113" t="n">
         <v>31</v>
       </c>
       <c r="F113" t="n">
-        <v>14.01589282674076</v>
+        <v>13.85792890742731</v>
       </c>
       <c r="G113" t="n">
-        <v>1.932209021795149</v>
+        <v>1.963482749965068</v>
       </c>
       <c r="H113" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I113" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J113" t="n">
-        <v>3.019705423636884e-07</v>
+        <v>3.225479547042006e-06</v>
       </c>
       <c r="K113" t="n">
-        <v>9.05911627091065e-06</v>
+        <v>9.676438641126016e-05</v>
       </c>
       <c r="L113" t="b">
         <v>1</v>
@@ -4968,31 +4980,31 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>15.51433205614264</v>
+        <v>15.14712856360899</v>
       </c>
       <c r="D114" t="n">
-        <v>2.710013521345731</v>
+        <v>3.258212284210873</v>
       </c>
       <c r="E114" t="n">
         <v>31</v>
       </c>
       <c r="F114" t="n">
-        <v>19.66561850916517</v>
+        <v>19.83569415281006</v>
       </c>
       <c r="G114" t="n">
-        <v>1.235081793364541</v>
+        <v>1.175657011202386</v>
       </c>
       <c r="H114" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I114" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="J114" t="n">
-        <v>6.127203739948178e-07</v>
+        <v>5.486251968345677e-07</v>
       </c>
       <c r="K114" t="n">
-        <v>1.838161121984454e-05</v>
+        <v>1.645875590503703e-05</v>
       </c>
       <c r="L114" t="b">
         <v>1</v>
@@ -5008,31 +5020,31 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>11.99821858449684</v>
+        <v>12.05908387353063</v>
       </c>
       <c r="D115" t="n">
-        <v>2.787023706666074</v>
+        <v>2.734643225814461</v>
       </c>
       <c r="E115" t="n">
         <v>31</v>
       </c>
       <c r="F115" t="n">
-        <v>16.89582784745468</v>
+        <v>16.61861352300595</v>
       </c>
       <c r="G115" t="n">
-        <v>2.055827984444404</v>
+        <v>1.977059885940042</v>
       </c>
       <c r="H115" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I115" t="n">
         <v>55</v>
       </c>
       <c r="J115" t="n">
-        <v>9.107953824183401e-07</v>
+        <v>3.566372324431282e-06</v>
       </c>
       <c r="K115" t="n">
-        <v>2.73238614725502e-05</v>
+        <v>0.0001069911697329385</v>
       </c>
       <c r="L115" t="b">
         <v>1</v>
@@ -5048,31 +5060,31 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>13.57015781206804</v>
+        <v>13.31024789885964</v>
       </c>
       <c r="D116" t="n">
-        <v>2.226983148449796</v>
+        <v>2.639913051820528</v>
       </c>
       <c r="E116" t="n">
         <v>31</v>
       </c>
       <c r="F116" t="n">
-        <v>19.66922450485213</v>
+        <v>19.71689595432214</v>
       </c>
       <c r="G116" t="n">
-        <v>1.635494483408771</v>
+        <v>1.650409198715037</v>
       </c>
       <c r="H116" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>2.356708487617561e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K116" t="n">
-        <v>7.070125462852682e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L116" t="b">
         <v>1</v>
@@ -5088,31 +5100,31 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>8.941277956470541</v>
+        <v>9.012883271609555</v>
       </c>
       <c r="D117" t="n">
-        <v>3.34646643432879</v>
+        <v>3.419051754717597</v>
       </c>
       <c r="E117" t="n">
         <v>31</v>
       </c>
       <c r="F117" t="n">
-        <v>18.71906042506095</v>
+        <v>18.69648966826193</v>
       </c>
       <c r="G117" t="n">
-        <v>2.569835323462818</v>
+        <v>2.707506934018686</v>
       </c>
       <c r="H117" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I117" t="n">
         <v>3</v>
       </c>
       <c r="J117" t="n">
-        <v>3.354961367286807e-09</v>
+        <v>1.106083286268991e-08</v>
       </c>
       <c r="K117" t="n">
-        <v>1.006488410186042e-07</v>
+        <v>3.318249858806974e-07</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -5128,31 +5140,31 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>10.81492591734596</v>
+        <v>10.4282435235078</v>
       </c>
       <c r="D118" t="n">
-        <v>3.490460468202385</v>
+        <v>3.534126001980839</v>
       </c>
       <c r="E118" t="n">
         <v>31</v>
       </c>
       <c r="F118" t="n">
-        <v>16.42830953696224</v>
+        <v>16.06392433950116</v>
       </c>
       <c r="G118" t="n">
-        <v>3.996585574654192</v>
+        <v>4.047494767268882</v>
       </c>
       <c r="H118" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I118" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J118" t="n">
-        <v>0.000109647476020256</v>
+        <v>0.0002321583819918567</v>
       </c>
       <c r="K118" t="n">
-        <v>0.003289424280607679</v>
+        <v>0.0069647514597557</v>
       </c>
       <c r="L118" t="b">
         <v>1</v>
@@ -5168,31 +5180,31 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>9.860089583650295</v>
+        <v>9.598185389631283</v>
       </c>
       <c r="D119" t="n">
-        <v>3.115607008199128</v>
+        <v>2.909113754261333</v>
       </c>
       <c r="E119" t="n">
         <v>31</v>
       </c>
       <c r="F119" t="n">
-        <v>21.14194776129968</v>
+        <v>21.1394136838576</v>
       </c>
       <c r="G119" t="n">
-        <v>1.801659434702326</v>
+        <v>1.898946371348081</v>
       </c>
       <c r="H119" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>2.356708487617561e-09</v>
+        <v>7.657877980059407e-09</v>
       </c>
       <c r="K119" t="n">
-        <v>7.070125462852682e-08</v>
+        <v>2.297363394017822e-07</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
@@ -5208,31 +5220,31 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>12.70726214252323</v>
+        <v>12.5349807568324</v>
       </c>
       <c r="D120" t="n">
-        <v>4.846684657225896</v>
+        <v>4.818984174604413</v>
       </c>
       <c r="E120" t="n">
         <v>31</v>
       </c>
       <c r="F120" t="n">
-        <v>17.17217906769212</v>
+        <v>16.28704663742478</v>
       </c>
       <c r="G120" t="n">
-        <v>5.101045851785213</v>
+        <v>4.590997519202081</v>
       </c>
       <c r="H120" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I120" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J120" t="n">
-        <v>0.01630830831692752</v>
+        <v>0.03906193301445199</v>
       </c>
       <c r="K120" t="n">
-        <v>0.4892492495078257</v>
+        <v>1</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5248,31 +5260,31 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>14.21766748044038</v>
+        <v>13.96928445025033</v>
       </c>
       <c r="D121" t="n">
-        <v>3.093659084026806</v>
+        <v>3.34978122659866</v>
       </c>
       <c r="E121" t="n">
         <v>31</v>
       </c>
       <c r="F121" t="n">
-        <v>17.67029200130309</v>
+        <v>17.42609322448693</v>
       </c>
       <c r="G121" t="n">
-        <v>1.820401274891514</v>
+        <v>1.726240253121041</v>
       </c>
       <c r="H121" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I121" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J121" t="n">
-        <v>6.778101584433548e-05</v>
+        <v>0.0001971375739483935</v>
       </c>
       <c r="K121" t="n">
-        <v>0.002033430475330065</v>
+        <v>0.005914127218451804</v>
       </c>
       <c r="L121" t="b">
         <v>1</v>
